--- a/evaluation_forms/041_junior_associate_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/041_junior_associate_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'first_90_days'}</t>
+          <t>first_90_days</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'First 90 days'}</t>
+          <t>First 90 days</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'next_90_days'}</t>
+          <t>next_90_days</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Next 90 days'}</t>
+          <t>Next 90 days</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'beyond_6_months'}</t>
+          <t>beyond_6_months</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Beyond 6 months'}</t>
+          <t>Beyond 6 months</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'initiative'}</t>
+          <t>initiative</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Initiative'}</t>
+          <t>Initiative</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'initiative'}</t>
+          <t>initiative</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Initiative'}</t>
+          <t>Initiative</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
